--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2019/American_Aircraft_Cumulative_Statistics_2019.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2019/American_Aircraft_Cumulative_Statistics_2019.xlsx
@@ -13,36 +13,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29" uniqueCount="29">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -124,10 +145,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -147,40 +168,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -188,40 +209,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>5640333089</v>
+        <v>1011539795</v>
       </c>
       <c r="C2" s="0">
-        <v>6685624840</v>
+        <v>1293269433</v>
       </c>
       <c r="D2" s="0">
-        <v>348210</v>
+        <v>206923</v>
       </c>
       <c r="E2" s="0">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="F2" s="0">
-        <v>40189</v>
+        <v>32122</v>
       </c>
       <c r="G2" s="0">
-        <v>2.0899999999999999</v>
+        <v>5.1399999999999997</v>
       </c>
       <c r="H2" s="0">
-        <v>6.2599999999999998</v>
+        <v>8.3599999999999994</v>
       </c>
       <c r="I2" s="0">
-        <v>84.370000000000005</v>
+        <v>78.219999999999999</v>
       </c>
       <c r="J2" s="0">
-        <v>1114</v>
+        <v>407</v>
       </c>
       <c r="K2" s="0">
-        <v>7054</v>
+        <v>2395.0900000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>47.259999999999998</v>
+        <v>24.190000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>0.13</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -229,40 +250,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>8369016479</v>
+        <v>15954443803</v>
       </c>
       <c r="C3" s="0">
-        <v>10070090451</v>
+        <v>18924706715</v>
       </c>
       <c r="D3" s="0">
-        <v>561008</v>
+        <v>439088</v>
       </c>
       <c r="E3" s="0">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="F3" s="0">
-        <v>63783</v>
+        <v>193316</v>
       </c>
       <c r="G3" s="0">
-        <v>3.5499999999999998</v>
+        <v>4.4900000000000002</v>
       </c>
       <c r="H3" s="0">
-        <v>8.0800000000000001</v>
+        <v>9.9900000000000002</v>
       </c>
       <c r="I3" s="0">
-        <v>83.109999999999999</v>
+        <v>84.299999999999997</v>
       </c>
       <c r="J3" s="0">
-        <v>869</v>
+        <v>765</v>
       </c>
       <c r="K3" s="0">
-        <v>3857</v>
+        <v>3636.3899999999999</v>
       </c>
       <c r="L3" s="0">
-        <v>21.239999999999998</v>
+        <v>28.41</v>
       </c>
       <c r="M3" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="4">
@@ -297,13 +318,13 @@
         <v>734</v>
       </c>
       <c r="K4" s="0">
-        <v>3918</v>
+        <v>3917.7800000000002</v>
       </c>
       <c r="L4" s="0">
         <v>26.120000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.076999999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -311,40 +332,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>10085080549</v>
+        <v>53739370654</v>
       </c>
       <c r="C5" s="0">
-        <v>11911860393</v>
+        <v>60713244791</v>
       </c>
       <c r="D5" s="0">
-        <v>533686</v>
+        <v>752146</v>
       </c>
       <c r="E5" s="0">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="F5" s="0">
-        <v>86870</v>
+        <v>267022</v>
       </c>
       <c r="G5" s="0">
-        <v>3.8900000000000001</v>
+        <v>3.3100000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>9.4900000000000002</v>
+        <v>10.84</v>
       </c>
       <c r="I5" s="0">
-        <v>84.659999999999997</v>
+        <v>88.510000000000005</v>
       </c>
       <c r="J5" s="0">
-        <v>874</v>
+        <v>1281</v>
       </c>
       <c r="K5" s="0">
-        <v>4140</v>
+        <v>5196.6800000000003</v>
       </c>
       <c r="L5" s="0">
-        <v>26.379999999999999</v>
+        <v>29.190000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -352,40 +373,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>5201579279</v>
+        <v>1036095305</v>
       </c>
       <c r="C6" s="0">
-        <v>6013737756</v>
+        <v>1193263656</v>
       </c>
       <c r="D6" s="0">
-        <v>793369</v>
+        <v>407257</v>
       </c>
       <c r="E6" s="0">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F6" s="0">
-        <v>31456</v>
+        <v>3716</v>
       </c>
       <c r="G6" s="0">
-        <v>4.1500000000000004</v>
+        <v>1.27</v>
       </c>
       <c r="H6" s="0">
-        <v>11.65</v>
+        <v>4.9699999999999998</v>
       </c>
       <c r="I6" s="0">
-        <v>86.489999999999995</v>
+        <v>86.829999999999998</v>
       </c>
       <c r="J6" s="0">
-        <v>1055</v>
+        <v>1639</v>
       </c>
       <c r="K6" s="0">
-        <v>3684</v>
+        <v>6626.7299999999996</v>
       </c>
       <c r="L6" s="0">
-        <v>20.32</v>
+        <v>33.82</v>
       </c>
       <c r="M6" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="7">
@@ -393,40 +414,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>28127491310</v>
+        <v>55709808772</v>
       </c>
       <c r="C7" s="0">
-        <v>33753877589</v>
+        <v>65137402268</v>
       </c>
       <c r="D7" s="0">
-        <v>711357</v>
+        <v>625780</v>
       </c>
       <c r="E7" s="0">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F7" s="0">
-        <v>180534</v>
+        <v>403416</v>
       </c>
       <c r="G7" s="0">
-        <v>3.7999999999999998</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>11.880000000000001</v>
+        <v>10.52</v>
       </c>
       <c r="I7" s="0">
-        <v>83.329999999999998</v>
+        <v>85.530000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>1225</v>
+        <v>992</v>
       </c>
       <c r="K7" s="0">
-        <v>4290</v>
+        <v>4465.5</v>
       </c>
       <c r="L7" s="0">
-        <v>28.109999999999999</v>
+        <v>27.449999999999999</v>
       </c>
       <c r="M7" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="8">
@@ -434,40 +455,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>16470145031</v>
+        <v>902639686</v>
       </c>
       <c r="C8" s="0">
-        <v>19652617114</v>
+        <v>1096442552</v>
       </c>
       <c r="D8" s="0">
-        <v>973384</v>
+        <v>726121</v>
       </c>
       <c r="E8" s="0">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F8" s="0">
-        <v>109028</v>
+        <v>5324</v>
       </c>
       <c r="G8" s="0">
-        <v>5.4000000000000004</v>
+        <v>3.5299999999999998</v>
       </c>
       <c r="H8" s="0">
-        <v>14.15</v>
+        <v>11.130000000000001</v>
       </c>
       <c r="I8" s="0">
-        <v>83.810000000000002</v>
+        <v>82.319999999999993</v>
       </c>
       <c r="J8" s="0">
-        <v>989</v>
+        <v>1197</v>
       </c>
       <c r="K8" s="0">
-        <v>2996</v>
+        <v>4706.96</v>
       </c>
       <c r="L8" s="0">
-        <v>16.43</v>
+        <v>27.370000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="9">
@@ -475,40 +496,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>16875340154</v>
+        <v>7236062161</v>
       </c>
       <c r="C9" s="0">
-        <v>19765669350</v>
+        <v>8238732597</v>
       </c>
       <c r="D9" s="0">
-        <v>549657</v>
+        <v>806928</v>
       </c>
       <c r="E9" s="0">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="F9" s="0">
-        <v>130168</v>
+        <v>27115</v>
       </c>
       <c r="G9" s="0">
-        <v>3.6200000000000001</v>
+        <v>2.6600000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>9.8800000000000008</v>
+        <v>10.789999999999999</v>
       </c>
       <c r="I9" s="0">
-        <v>85.379999999999995</v>
+        <v>87.829999999999998</v>
       </c>
       <c r="J9" s="0">
-        <v>1012</v>
+        <v>1703</v>
       </c>
       <c r="K9" s="0">
-        <v>4253</v>
+        <v>5874.1099999999997</v>
       </c>
       <c r="L9" s="0">
-        <v>28.359999999999999</v>
+        <v>32.93</v>
       </c>
       <c r="M9" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -516,40 +537,327 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>97547997188</v>
+        <v>5368266318</v>
       </c>
       <c r="C10" s="0">
-        <v>115846730618</v>
+        <v>6368708444</v>
       </c>
       <c r="D10" s="0">
-        <v>650349</v>
+        <v>1028871</v>
       </c>
       <c r="E10" s="0">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="F10" s="0">
-        <v>714600</v>
+        <v>13494</v>
       </c>
       <c r="G10" s="0">
-        <v>4.0099999999999998</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>10.82</v>
+        <v>11.34</v>
       </c>
       <c r="I10" s="0">
-        <v>84.200000000000003</v>
+        <v>84.290000000000006</v>
       </c>
       <c r="J10" s="0">
-        <v>1012</v>
+        <v>2290</v>
       </c>
       <c r="K10" s="0">
-        <v>4156</v>
+        <v>7380.4499999999998</v>
       </c>
       <c r="L10" s="0">
-        <v>25.969999999999999</v>
+        <v>35.780000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.081000000000000003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>5729094114</v>
+      </c>
+      <c r="C11" s="0">
+        <v>7019909387</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1503193</v>
+      </c>
+      <c r="E11" s="0">
+        <v>243</v>
+      </c>
+      <c r="F11" s="0">
+        <v>9019</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1.9299999999999999</v>
+      </c>
+      <c r="H11" s="0">
+        <v>13.369999999999999</v>
+      </c>
+      <c r="I11" s="0">
+        <v>81.609999999999999</v>
+      </c>
+      <c r="J11" s="0">
+        <v>3208</v>
+      </c>
+      <c r="K11" s="0">
+        <v>8864</v>
+      </c>
+      <c r="L11" s="0">
+        <v>36.520000000000003</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.079000000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>4076680722</v>
+      </c>
+      <c r="C12" s="0">
+        <v>5109715634</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1892487</v>
+      </c>
+      <c r="E12" s="0">
+        <v>287</v>
+      </c>
+      <c r="F12" s="0">
+        <v>4934</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1.8300000000000001</v>
+      </c>
+      <c r="H12" s="0">
+        <v>14.18</v>
+      </c>
+      <c r="I12" s="0">
+        <v>79.780000000000001</v>
+      </c>
+      <c r="J12" s="0">
+        <v>3612</v>
+      </c>
+      <c r="K12" s="0">
+        <v>10174.200000000001</v>
+      </c>
+      <c r="L12" s="0">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.075999999999999998</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>7573229281</v>
+      </c>
+      <c r="C13" s="0">
+        <v>9041640563</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1492020</v>
+      </c>
+      <c r="E13" s="0">
+        <v>233</v>
+      </c>
+      <c r="F13" s="0">
+        <v>11302</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1.8700000000000001</v>
+      </c>
+      <c r="H13" s="0">
+        <v>13.31</v>
+      </c>
+      <c r="I13" s="0">
+        <v>83.760000000000005</v>
+      </c>
+      <c r="J13" s="0">
+        <v>3436</v>
+      </c>
+      <c r="K13" s="0">
+        <v>8490.0200000000004</v>
+      </c>
+      <c r="L13" s="0">
+        <v>36.469999999999999</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0.075999999999999998</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>12138378091</v>
+      </c>
+      <c r="C14" s="0">
+        <v>14488437658</v>
+      </c>
+      <c r="D14" s="0">
+        <v>2232425</v>
+      </c>
+      <c r="E14" s="0">
+        <v>285</v>
+      </c>
+      <c r="F14" s="0">
+        <v>10324</v>
+      </c>
+      <c r="G14" s="0">
+        <v>1.5900000000000001</v>
+      </c>
+      <c r="H14" s="0">
+        <v>15.67</v>
+      </c>
+      <c r="I14" s="0">
+        <v>83.780000000000001</v>
+      </c>
+      <c r="J14" s="0">
+        <v>4935</v>
+      </c>
+      <c r="K14" s="0">
+        <v>10345.18</v>
+      </c>
+      <c r="L14" s="0">
+        <v>36.380000000000003</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0.072999999999999995</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0">
+        <v>21787948500</v>
+      </c>
+      <c r="C15" s="0">
+        <v>25917264340</v>
+      </c>
+      <c r="D15" s="0">
+        <v>1796068</v>
+      </c>
+      <c r="E15" s="0">
+        <v>272</v>
+      </c>
+      <c r="F15" s="0">
+        <v>23850</v>
+      </c>
+      <c r="G15" s="0">
+        <v>1.6499999999999999</v>
+      </c>
+      <c r="H15" s="0">
+        <v>13.56</v>
+      </c>
+      <c r="I15" s="0">
+        <v>84.069999999999993</v>
+      </c>
+      <c r="J15" s="0">
+        <v>3996</v>
+      </c>
+      <c r="K15" s="0">
+        <v>10778.32</v>
+      </c>
+      <c r="L15" s="0">
+        <v>39.630000000000003</v>
+      </c>
+      <c r="M15" s="0">
+        <v>0.081000000000000003</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0">
+        <v>11796254231</v>
+      </c>
+      <c r="C16" s="0">
+        <v>13873180354</v>
+      </c>
+      <c r="D16" s="0">
+        <v>2205593</v>
+      </c>
+      <c r="E16" s="0">
+        <v>304</v>
+      </c>
+      <c r="F16" s="0">
+        <v>9263</v>
+      </c>
+      <c r="G16" s="0">
+        <v>1.47</v>
+      </c>
+      <c r="H16" s="0">
+        <v>14.58</v>
+      </c>
+      <c r="I16" s="0">
+        <v>85.030000000000001</v>
+      </c>
+      <c r="J16" s="0">
+        <v>4927</v>
+      </c>
+      <c r="K16" s="0">
+        <v>12444.700000000001</v>
+      </c>
+      <c r="L16" s="0">
+        <v>40.939999999999998</v>
+      </c>
+      <c r="M16" s="0">
+        <v>0.082000000000000003</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0">
+        <v>210838822730</v>
+      </c>
+      <c r="C17" s="0">
+        <v>246409171517</v>
+      </c>
+      <c r="D17" s="0">
+        <v>812910</v>
+      </c>
+      <c r="E17" s="0">
+        <v>166</v>
+      </c>
+      <c r="F17" s="0">
+        <v>1086789</v>
+      </c>
+      <c r="G17" s="0">
+        <v>3.5899999999999999</v>
+      </c>
+      <c r="H17" s="0">
+        <v>11.19</v>
+      </c>
+      <c r="I17" s="0">
+        <v>85.560000000000002</v>
+      </c>
+      <c r="J17" s="0">
+        <v>1218</v>
+      </c>
+      <c r="K17" s="0">
+        <v>5605.1499999999996</v>
+      </c>
+      <c r="L17" s="0">
+        <v>31.039999999999999</v>
+      </c>
+      <c r="M17" s="0">
+        <v>0.076999999999999999</v>
       </c>
     </row>
   </sheetData>
